--- a/scripts/template_meta_suggestions.xlsx
+++ b/scripts/template_meta_suggestions.xlsx
@@ -101,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="20" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -114,6 +114,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -538,6 +541,11 @@
           <t>Suggested H1</t>
         </is>
       </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Content-Keyword Match</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
